--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260609.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,191,000</t>
+          <t>2,492,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,492,000</t>
+          <t>5,191,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,761,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>1,761,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>422,000</t>
+          <t>686,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>686,000</t>
+          <t>422,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1745,42 +1745,20 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-31,149,152</t>
+          <t>-1,329,352,813</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-1,329,352,813</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>-0.46%</t>
         </is>
